--- a/data/auto_synced/Financial_Model_25MT_Gujarat.xlsx
+++ b/data/auto_synced/Financial_Model_25MT_Gujarat.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04 April 2026</t>
+          <t>05 April 2026</t>
         </is>
       </c>
     </row>
